--- a/numerical-workflows/v2/framework/06_最终配置/爬塔/UIlevel.xlsx
+++ b/numerical-workflows/v2/framework/06_最终配置/爬塔/UIlevel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="level" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="中文说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="level" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中文说明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ404"/>
+  <dimension ref="A1:AQ504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.2222222222222" customWidth="1" min="2" max="2"/>
@@ -1907,7 +1907,7 @@
       <c r="Q14" s="39" t="n"/>
       <c r="R14" s="39" t="inlineStr">
         <is>
-          <t>1074,55;103,1;2,300</t>
+          <t>1074,55;106,5;2,300</t>
         </is>
       </c>
       <c r="S14" s="40" t="inlineStr">
@@ -2571,7 +2571,7 @@
       <c r="Q24" s="39" t="n"/>
       <c r="R24" s="39" t="inlineStr">
         <is>
-          <t>1074,60;103,1;2,350</t>
+          <t>1074,60;106,5;2,350</t>
         </is>
       </c>
       <c r="S24" s="40" t="inlineStr">
@@ -3235,7 +3235,7 @@
       <c r="Q34" s="39" t="n"/>
       <c r="R34" s="39" t="inlineStr">
         <is>
-          <t>1074,80;103,1;2,350;3027,50</t>
+          <t>1074,80;106,5;2,350;3027,150</t>
         </is>
       </c>
       <c r="S34" s="40" t="inlineStr">
@@ -3899,7 +3899,7 @@
       <c r="Q44" s="39" t="n"/>
       <c r="R44" s="39" t="inlineStr">
         <is>
-          <t>1074,90;103,1;2,400;3027,75</t>
+          <t>1074,90;103,1;2,400;1156,20;1157,1</t>
         </is>
       </c>
       <c r="S44" s="40" t="inlineStr">
@@ -4563,7 +4563,7 @@
       <c r="Q54" s="39" t="n"/>
       <c r="R54" s="39" t="inlineStr">
         <is>
-          <t>1074,100;103,1;2,450;3027,100</t>
+          <t>1074,100;103,1;2,450;1156,25;1157,1</t>
         </is>
       </c>
       <c r="S54" s="40" t="inlineStr">
@@ -5222,7 +5222,7 @@
       <c r="Q64" s="39" t="n"/>
       <c r="R64" s="39" t="inlineStr">
         <is>
-          <t>1074,120;103,1;2,450;3027,125</t>
+          <t>1074,120;103,1;2,450;3027,200</t>
         </is>
       </c>
       <c r="S64" s="40" t="inlineStr">
@@ -5884,7 +5884,7 @@
       <c r="Q74" s="39" t="n"/>
       <c r="R74" s="39" t="inlineStr">
         <is>
-          <t>1074,140;103,1;2,500;3027,150</t>
+          <t>1074,140;103,1;2,500;1156,30;1157,2</t>
         </is>
       </c>
       <c r="S74" s="40" t="inlineStr">
@@ -6522,7 +6522,7 @@
       <c r="Q84" s="39" t="n"/>
       <c r="R84" s="39" t="inlineStr">
         <is>
-          <t>1074,155;103,1;2,550;3027,175</t>
+          <t>1074,155;103,1;2,550;1156,35;1157,3</t>
         </is>
       </c>
       <c r="S84" s="40" t="inlineStr">
@@ -7174,7 +7174,7 @@
       <c r="Q94" s="39" t="n"/>
       <c r="R94" s="39" t="inlineStr">
         <is>
-          <t>1074,180;103,1;2,550;3027,225</t>
+          <t>1074,180;103,1;2,550;1156,40;1157,3</t>
         </is>
       </c>
       <c r="S94" s="40" t="inlineStr">
@@ -8482,7 +8482,7 @@
       <c r="Q114" s="39" t="n"/>
       <c r="R114" s="39" t="inlineStr">
         <is>
-          <t>1074,55;103,1;2,300</t>
+          <t>1074,55;106,5;2,300</t>
         </is>
       </c>
       <c r="S114" s="40" t="inlineStr">
@@ -9126,7 +9126,7 @@
       <c r="Q124" s="39" t="n"/>
       <c r="R124" s="39" t="inlineStr">
         <is>
-          <t>1074,60;103,1;2,350</t>
+          <t>1074,60;106,5;2,350</t>
         </is>
       </c>
       <c r="S124" s="40" t="inlineStr">
@@ -9770,7 +9770,7 @@
       <c r="Q134" s="39" t="n"/>
       <c r="R134" s="39" t="inlineStr">
         <is>
-          <t>1074,80;103,1;2,350;3027,50</t>
+          <t>1074,80;106,5;2,350;3027,150</t>
         </is>
       </c>
       <c r="S134" s="40" t="inlineStr">
@@ -10414,7 +10414,7 @@
       <c r="Q144" s="39" t="n"/>
       <c r="R144" s="39" t="inlineStr">
         <is>
-          <t>1074,90;103,1;2,400;3027,75</t>
+          <t>1074,90;103,1;2,400;1156,20;1157,1</t>
         </is>
       </c>
       <c r="S144" s="40" t="inlineStr">
@@ -11058,7 +11058,7 @@
       <c r="Q154" s="39" t="n"/>
       <c r="R154" s="39" t="inlineStr">
         <is>
-          <t>1074,100;103,1;2,450;3027,100</t>
+          <t>1074,100;103,1;2,450;1156,25;1157,1</t>
         </is>
       </c>
       <c r="S154" s="40" t="inlineStr">
@@ -11702,7 +11702,7 @@
       <c r="Q164" s="39" t="n"/>
       <c r="R164" s="39" t="inlineStr">
         <is>
-          <t>1074,120;103,1;2,450;3027,125</t>
+          <t>1074,120;103,1;2,450;3027,200</t>
         </is>
       </c>
       <c r="S164" s="40" t="inlineStr">
@@ -12346,7 +12346,7 @@
       <c r="Q174" s="39" t="n"/>
       <c r="R174" s="39" t="inlineStr">
         <is>
-          <t>1074,140;103,1;2,500;3027,150</t>
+          <t>1074,140;103,1;2,500;1156,30;1157,2</t>
         </is>
       </c>
       <c r="S174" s="40" t="inlineStr">
@@ -12990,7 +12990,7 @@
       <c r="Q184" s="39" t="n"/>
       <c r="R184" s="39" t="inlineStr">
         <is>
-          <t>1074,155;103,1;2,550;3027,175</t>
+          <t>1074,155;103,1;2,550;1156,35;1157,3</t>
         </is>
       </c>
       <c r="S184" s="40" t="inlineStr">
@@ -13634,7 +13634,7 @@
       <c r="Q194" s="39" t="n"/>
       <c r="R194" s="39" t="inlineStr">
         <is>
-          <t>1074,180;103,1;2,550;3027,225</t>
+          <t>1074,180;103,1;2,550;1156,40;1157,3</t>
         </is>
       </c>
       <c r="S194" s="40" t="inlineStr">
@@ -14922,7 +14922,7 @@
       <c r="Q214" s="39" t="n"/>
       <c r="R214" s="39" t="inlineStr">
         <is>
-          <t>1074,55;103,1;2,300</t>
+          <t>1074,55;106,5;2,300</t>
         </is>
       </c>
       <c r="S214" s="40" t="inlineStr">
@@ -15566,7 +15566,7 @@
       <c r="Q224" s="39" t="n"/>
       <c r="R224" s="39" t="inlineStr">
         <is>
-          <t>1074,60;103,1;2,350</t>
+          <t>1074,60;106,5;2,350</t>
         </is>
       </c>
       <c r="S224" s="40" t="inlineStr">
@@ -16210,7 +16210,7 @@
       <c r="Q234" s="39" t="n"/>
       <c r="R234" s="39" t="inlineStr">
         <is>
-          <t>1074,80;103,1;2,350;3027,50</t>
+          <t>1074,80;106,5;2,350;3027,150</t>
         </is>
       </c>
       <c r="S234" s="40" t="inlineStr">
@@ -16854,7 +16854,7 @@
       <c r="Q244" s="39" t="n"/>
       <c r="R244" s="39" t="inlineStr">
         <is>
-          <t>1074,90;103,1;2,400;3027,75</t>
+          <t>1074,90;103,1;2,400;1156,20;1157,1</t>
         </is>
       </c>
       <c r="S244" s="40" t="inlineStr">
@@ -17498,7 +17498,7 @@
       <c r="Q254" s="39" t="n"/>
       <c r="R254" s="39" t="inlineStr">
         <is>
-          <t>1074,100;103,1;2,450;3027,100</t>
+          <t>1074,100;103,1;2,450;1156,25;1157,1</t>
         </is>
       </c>
       <c r="S254" s="40" t="inlineStr">
@@ -18142,7 +18142,7 @@
       <c r="Q264" s="39" t="n"/>
       <c r="R264" s="39" t="inlineStr">
         <is>
-          <t>1074,120;103,1;2,450;3027,125</t>
+          <t>1074,120;103,1;2,450;3027,200</t>
         </is>
       </c>
       <c r="S264" s="40" t="inlineStr">
@@ -18786,7 +18786,7 @@
       <c r="Q274" s="39" t="n"/>
       <c r="R274" s="39" t="inlineStr">
         <is>
-          <t>1074,140;103,1;2,500;3027,150</t>
+          <t>1074,140;103,1;2,500;1156,30;1157,2</t>
         </is>
       </c>
       <c r="S274" s="40" t="inlineStr">
@@ -19430,7 +19430,7 @@
       <c r="Q284" s="39" t="n"/>
       <c r="R284" s="39" t="inlineStr">
         <is>
-          <t>1074,155;103,1;2,550;3027,175</t>
+          <t>1074,155;103,1;2,550;1156,35;1157,3</t>
         </is>
       </c>
       <c r="S284" s="40" t="inlineStr">
@@ -20074,7 +20074,7 @@
       <c r="Q294" s="39" t="n"/>
       <c r="R294" s="39" t="inlineStr">
         <is>
-          <t>1074,180;103,1;2,550;3027,225</t>
+          <t>1074,180;103,1;2,550;1156,40;1157,3</t>
         </is>
       </c>
       <c r="S294" s="40" t="inlineStr">
@@ -21362,7 +21362,7 @@
       <c r="Q314" s="39" t="n"/>
       <c r="R314" s="39" t="inlineStr">
         <is>
-          <t>1074,55;103,1;2,300</t>
+          <t>1074,55;106,5;2,300</t>
         </is>
       </c>
       <c r="S314" s="40" t="inlineStr">
@@ -22006,7 +22006,7 @@
       <c r="Q324" s="39" t="n"/>
       <c r="R324" s="39" t="inlineStr">
         <is>
-          <t>1074,60;103,1;2,350</t>
+          <t>1074,60;106,5;2,350</t>
         </is>
       </c>
       <c r="S324" s="40" t="inlineStr">
@@ -22650,7 +22650,7 @@
       <c r="Q334" s="39" t="n"/>
       <c r="R334" s="39" t="inlineStr">
         <is>
-          <t>1074,80;103,1;2,350;3027,50</t>
+          <t>1074,80;106,5;2,350;3027,150</t>
         </is>
       </c>
       <c r="S334" s="40" t="inlineStr">
@@ -23294,7 +23294,7 @@
       <c r="Q344" s="39" t="n"/>
       <c r="R344" s="39" t="inlineStr">
         <is>
-          <t>1074,90;103,1;2,400;3027,75</t>
+          <t>1074,90;103,1;2,400;1156,20;1157,1</t>
         </is>
       </c>
       <c r="S344" s="40" t="inlineStr">
@@ -23938,7 +23938,7 @@
       <c r="Q354" s="39" t="n"/>
       <c r="R354" s="39" t="inlineStr">
         <is>
-          <t>1074,100;103,1;2,450;3027,100</t>
+          <t>1074,100;103,1;2,450;1156,25;1157,1</t>
         </is>
       </c>
       <c r="S354" s="40" t="inlineStr">
@@ -24582,7 +24582,7 @@
       <c r="Q364" s="39" t="n"/>
       <c r="R364" s="39" t="inlineStr">
         <is>
-          <t>1074,120;103,1;2,450;3027,125</t>
+          <t>1074,120;103,1;2,450;3027,200</t>
         </is>
       </c>
       <c r="S364" s="40" t="inlineStr">
@@ -25226,7 +25226,7 @@
       <c r="Q374" s="39" t="n"/>
       <c r="R374" s="39" t="inlineStr">
         <is>
-          <t>1074,140;103,1;2,500;3027,150</t>
+          <t>1074,140;103,1;2,500;1156,30;1157,2</t>
         </is>
       </c>
       <c r="S374" s="40" t="inlineStr">
@@ -25870,7 +25870,7 @@
       <c r="Q384" s="39" t="n"/>
       <c r="R384" s="39" t="inlineStr">
         <is>
-          <t>1074,155;103,1;2,550;3027,175</t>
+          <t>1074,155;103,1;2,550;1156,35;1157,3</t>
         </is>
       </c>
       <c r="S384" s="40" t="inlineStr">
@@ -26514,7 +26514,7 @@
       <c r="Q394" s="39" t="n"/>
       <c r="R394" s="39" t="inlineStr">
         <is>
-          <t>1074,180;103,1;2,550;3027,225</t>
+          <t>1074,180;103,1;2,550;1156,40;1157,3</t>
         </is>
       </c>
       <c r="S394" s="40" t="inlineStr">
@@ -27193,6 +27193,3606 @@
         <is>
           <t>20009;30104</t>
         </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="B405" t="n">
+        <v>300401</v>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>思考层-侵入1级</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I405" t="n">
+        <v>1</v>
+      </c>
+      <c r="R405" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S405" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T405" t="n">
+        <v>24000101</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="B406" t="n">
+        <v>300402</v>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>思考层-侵入2级</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I406" t="n">
+        <v>2</v>
+      </c>
+      <c r="R406" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S406" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T406" t="n">
+        <v>24000102</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="B407" t="n">
+        <v>300403</v>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>思考层-侵入3级</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I407" t="n">
+        <v>3</v>
+      </c>
+      <c r="R407" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S407" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T407" t="n">
+        <v>24000103</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="B408" t="n">
+        <v>300404</v>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>思考层-侵入4级</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I408" t="n">
+        <v>4</v>
+      </c>
+      <c r="R408" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S408" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T408" t="n">
+        <v>24000104</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="B409" t="n">
+        <v>300405</v>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>思考层-侵入5级</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I409" t="n">
+        <v>5</v>
+      </c>
+      <c r="R409" t="inlineStr">
+        <is>
+          <t>1074,180;106,6</t>
+        </is>
+      </c>
+      <c r="S409" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T409" t="n">
+        <v>24000105</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="B410" t="n">
+        <v>300406</v>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>思考层-侵入6级</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I410" t="n">
+        <v>6</v>
+      </c>
+      <c r="R410" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S410" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T410" t="n">
+        <v>24000106</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="B411" t="n">
+        <v>300407</v>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>思考层-侵入7级</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I411" t="n">
+        <v>7</v>
+      </c>
+      <c r="R411" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S411" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T411" t="n">
+        <v>24000107</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="B412" t="n">
+        <v>300408</v>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>思考层-侵入8级</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I412" t="n">
+        <v>8</v>
+      </c>
+      <c r="R412" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S412" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T412" t="n">
+        <v>24000108</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="B413" t="n">
+        <v>300409</v>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>思考层-侵入9级</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I413" t="n">
+        <v>9</v>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S413" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T413" t="n">
+        <v>24000109</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="B414" t="n">
+        <v>300410</v>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>思考层-侵入10级</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I414" t="n">
+        <v>10</v>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>1074,280;103,1;2,600</t>
+        </is>
+      </c>
+      <c r="S414" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T414" t="n">
+        <v>24000110</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="B415" t="n">
+        <v>300411</v>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>情绪层-侵入11级</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I415" t="n">
+        <v>11</v>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S415" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T415" t="n">
+        <v>24000111</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="B416" t="n">
+        <v>300412</v>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>情绪层-侵入12级</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I416" t="n">
+        <v>12</v>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S416" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T416" t="n">
+        <v>24000112</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="B417" t="n">
+        <v>300413</v>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>情绪层-侵入13级</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I417" t="n">
+        <v>13</v>
+      </c>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S417" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T417" t="n">
+        <v>24000113</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="B418" t="n">
+        <v>300414</v>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>情绪层-侵入14级</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I418" t="n">
+        <v>14</v>
+      </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S418" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T418" t="n">
+        <v>24000114</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="B419" t="n">
+        <v>300415</v>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>情绪层-侵入15级</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I419" t="n">
+        <v>15</v>
+      </c>
+      <c r="R419" t="inlineStr">
+        <is>
+          <t>1074,180;106,6</t>
+        </is>
+      </c>
+      <c r="S419" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T419" t="n">
+        <v>24000115</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="B420" t="n">
+        <v>300416</v>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>情绪层-侵入16级</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I420" t="n">
+        <v>16</v>
+      </c>
+      <c r="R420" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S420" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T420" t="n">
+        <v>24000116</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="B421" t="n">
+        <v>300417</v>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>情绪层-侵入17级</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I421" t="n">
+        <v>17</v>
+      </c>
+      <c r="R421" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S421" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T421" t="n">
+        <v>24000117</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="B422" t="n">
+        <v>300418</v>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>情绪层-侵入18级</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I422" t="n">
+        <v>18</v>
+      </c>
+      <c r="R422" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S422" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T422" t="n">
+        <v>24000118</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="B423" t="n">
+        <v>300419</v>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>情绪层-侵入19级</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I423" t="n">
+        <v>19</v>
+      </c>
+      <c r="R423" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S423" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T423" t="n">
+        <v>24000119</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="B424" t="n">
+        <v>300420</v>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>情绪层-侵入20级</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I424" t="n">
+        <v>20</v>
+      </c>
+      <c r="R424" t="inlineStr">
+        <is>
+          <t>1074,280;103,1;2,600;1156,40;1157,3</t>
+        </is>
+      </c>
+      <c r="S424" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T424" t="n">
+        <v>24000120</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="B425" t="n">
+        <v>300421</v>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>感知层-侵入21级</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I425" t="n">
+        <v>21</v>
+      </c>
+      <c r="R425" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S425" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T425" t="n">
+        <v>24000121</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="B426" t="n">
+        <v>300422</v>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>感知层-侵入22级</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I426" t="n">
+        <v>22</v>
+      </c>
+      <c r="R426" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S426" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T426" t="n">
+        <v>24000122</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="B427" t="n">
+        <v>300423</v>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>感知层-侵入23级</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I427" t="n">
+        <v>23</v>
+      </c>
+      <c r="R427" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S427" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T427" t="n">
+        <v>24000123</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="B428" t="n">
+        <v>300424</v>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>感知层-侵入24级</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I428" t="n">
+        <v>24</v>
+      </c>
+      <c r="R428" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S428" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T428" t="n">
+        <v>24000124</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="B429" t="n">
+        <v>300425</v>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>感知层-侵入25级</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I429" t="n">
+        <v>25</v>
+      </c>
+      <c r="R429" t="inlineStr">
+        <is>
+          <t>1074,180;106,6</t>
+        </is>
+      </c>
+      <c r="S429" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T429" t="n">
+        <v>24000125</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="B430" t="n">
+        <v>300426</v>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>感知层-侵入26级</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I430" t="n">
+        <v>26</v>
+      </c>
+      <c r="R430" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S430" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T430" t="n">
+        <v>24000126</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="B431" t="n">
+        <v>300427</v>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>感知层-侵入27级</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I431" t="n">
+        <v>27</v>
+      </c>
+      <c r="R431" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S431" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T431" t="n">
+        <v>24000127</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="B432" t="n">
+        <v>300428</v>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>感知层-侵入28级</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I432" t="n">
+        <v>28</v>
+      </c>
+      <c r="R432" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S432" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T432" t="n">
+        <v>24000128</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="B433" t="n">
+        <v>300429</v>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>感知层-侵入29级</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I433" t="n">
+        <v>29</v>
+      </c>
+      <c r="R433" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S433" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T433" t="n">
+        <v>24000129</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="B434" t="n">
+        <v>300430</v>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>感知层-侵入30级</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I434" t="n">
+        <v>30</v>
+      </c>
+      <c r="R434" t="inlineStr">
+        <is>
+          <t>1074,280;103,1;2,600;3027,300</t>
+        </is>
+      </c>
+      <c r="S434" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T434" t="n">
+        <v>24000130</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="B435" t="n">
+        <v>300431</v>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>前意识层-侵入31级</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I435" t="n">
+        <v>31</v>
+      </c>
+      <c r="R435" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S435" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T435" t="n">
+        <v>24000131</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="B436" t="n">
+        <v>300432</v>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>前意识层-侵入32级</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I436" t="n">
+        <v>32</v>
+      </c>
+      <c r="R436" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S436" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T436" t="n">
+        <v>24000132</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="B437" t="n">
+        <v>300433</v>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>前意识层-侵入33级</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I437" t="n">
+        <v>33</v>
+      </c>
+      <c r="R437" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S437" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T437" t="n">
+        <v>24000133</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="B438" t="n">
+        <v>300434</v>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>前意识层-侵入34级</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I438" t="n">
+        <v>34</v>
+      </c>
+      <c r="R438" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S438" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T438" t="n">
+        <v>24000134</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="B439" t="n">
+        <v>300435</v>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>前意识层-侵入35级</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I439" t="n">
+        <v>35</v>
+      </c>
+      <c r="R439" t="inlineStr">
+        <is>
+          <t>1074,180;106,6</t>
+        </is>
+      </c>
+      <c r="S439" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T439" t="n">
+        <v>24000135</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="B440" t="n">
+        <v>300436</v>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>前意识层-侵入36级</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I440" t="n">
+        <v>36</v>
+      </c>
+      <c r="R440" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S440" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T440" t="n">
+        <v>24000136</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="B441" t="n">
+        <v>300437</v>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>前意识层-侵入37级</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I441" t="n">
+        <v>37</v>
+      </c>
+      <c r="R441" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S441" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T441" t="n">
+        <v>24000137</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="B442" t="n">
+        <v>300438</v>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>前意识层-侵入38级</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I442" t="n">
+        <v>38</v>
+      </c>
+      <c r="R442" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S442" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T442" t="n">
+        <v>24000138</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="B443" t="n">
+        <v>300439</v>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>前意识层-侵入39级</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I443" t="n">
+        <v>39</v>
+      </c>
+      <c r="R443" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S443" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T443" t="n">
+        <v>24000139</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="B444" t="n">
+        <v>300440</v>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>前意识层-侵入40级</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I444" t="n">
+        <v>40</v>
+      </c>
+      <c r="R444" t="inlineStr">
+        <is>
+          <t>1074,280;103,1;2,600;1156,40;1157,3</t>
+        </is>
+      </c>
+      <c r="S444" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T444" t="n">
+        <v>24000140</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="B445" t="n">
+        <v>300441</v>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>人格面具-侵入41级</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I445" t="n">
+        <v>41</v>
+      </c>
+      <c r="R445" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S445" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T445" t="n">
+        <v>24000141</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="B446" t="n">
+        <v>300442</v>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>人格面具-侵入42级</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I446" t="n">
+        <v>42</v>
+      </c>
+      <c r="R446" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S446" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T446" t="n">
+        <v>24000142</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="B447" t="n">
+        <v>300443</v>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>人格面具-侵入43级</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I447" t="n">
+        <v>43</v>
+      </c>
+      <c r="R447" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S447" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T447" t="n">
+        <v>24000143</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="B448" t="n">
+        <v>300444</v>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>人格面具-侵入44级</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I448" t="n">
+        <v>44</v>
+      </c>
+      <c r="R448" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S448" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T448" t="n">
+        <v>24000144</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="B449" t="n">
+        <v>300445</v>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>人格面具-侵入45级</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I449" t="n">
+        <v>45</v>
+      </c>
+      <c r="R449" t="inlineStr">
+        <is>
+          <t>1074,180;106,6</t>
+        </is>
+      </c>
+      <c r="S449" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T449" t="n">
+        <v>24000145</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="B450" t="n">
+        <v>300446</v>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>人格面具-侵入46级</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I450" t="n">
+        <v>46</v>
+      </c>
+      <c r="R450" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S450" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T450" t="n">
+        <v>24000146</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="B451" t="n">
+        <v>300447</v>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>人格面具-侵入47级</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I451" t="n">
+        <v>47</v>
+      </c>
+      <c r="R451" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S451" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T451" t="n">
+        <v>24000147</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="B452" t="n">
+        <v>300448</v>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>人格面具-侵入48级</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I452" t="n">
+        <v>48</v>
+      </c>
+      <c r="R452" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S452" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T452" t="n">
+        <v>24000148</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="B453" t="n">
+        <v>300449</v>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>人格面具-侵入49级</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I453" t="n">
+        <v>49</v>
+      </c>
+      <c r="R453" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S453" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T453" t="n">
+        <v>24000149</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="B454" t="n">
+        <v>300450</v>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>人格面具-侵入50级</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I454" t="n">
+        <v>50</v>
+      </c>
+      <c r="R454" t="inlineStr">
+        <is>
+          <t>1074,280;103,1;2,600</t>
+        </is>
+      </c>
+      <c r="S454" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T454" t="n">
+        <v>24000150</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="B455" t="n">
+        <v>300451</v>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>涌动欲望-侵入51级</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I455" t="n">
+        <v>51</v>
+      </c>
+      <c r="R455" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S455" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T455" t="n">
+        <v>24000151</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="B456" t="n">
+        <v>300452</v>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>涌动欲望-侵入52级</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I456" t="n">
+        <v>52</v>
+      </c>
+      <c r="R456" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S456" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T456" t="n">
+        <v>24000152</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="B457" t="n">
+        <v>300453</v>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>涌动欲望-侵入53级</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I457" t="n">
+        <v>53</v>
+      </c>
+      <c r="R457" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S457" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T457" t="n">
+        <v>24000153</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="B458" t="n">
+        <v>300454</v>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>涌动欲望-侵入54级</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I458" t="n">
+        <v>54</v>
+      </c>
+      <c r="R458" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S458" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T458" t="n">
+        <v>24000154</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="B459" t="n">
+        <v>300455</v>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>涌动欲望-侵入55级</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I459" t="n">
+        <v>55</v>
+      </c>
+      <c r="R459" t="inlineStr">
+        <is>
+          <t>1074,180;106,6</t>
+        </is>
+      </c>
+      <c r="S459" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T459" t="n">
+        <v>24000155</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="B460" t="n">
+        <v>300456</v>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>涌动欲望-侵入56级</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I460" t="n">
+        <v>56</v>
+      </c>
+      <c r="R460" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S460" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T460" t="n">
+        <v>24000156</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="B461" t="n">
+        <v>300457</v>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>涌动欲望-侵入57级</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I461" t="n">
+        <v>57</v>
+      </c>
+      <c r="R461" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S461" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T461" t="n">
+        <v>24000157</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="B462" t="n">
+        <v>300458</v>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>涌动欲望-侵入58级</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I462" t="n">
+        <v>58</v>
+      </c>
+      <c r="R462" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S462" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T462" t="n">
+        <v>24000158</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="B463" t="n">
+        <v>300459</v>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>涌动欲望-侵入59级</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I463" t="n">
+        <v>59</v>
+      </c>
+      <c r="R463" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S463" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T463" t="n">
+        <v>24000159</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="B464" t="n">
+        <v>300460</v>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>涌动欲望-侵入60级</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I464" t="n">
+        <v>60</v>
+      </c>
+      <c r="R464" t="inlineStr">
+        <is>
+          <t>1074,280;103,1;2,600;1156,40;1157,3;3027,300</t>
+        </is>
+      </c>
+      <c r="S464" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T464" t="n">
+        <v>24000160</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="B465" t="n">
+        <v>300461</v>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>阴影岛屿-侵入61级</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I465" t="n">
+        <v>61</v>
+      </c>
+      <c r="R465" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S465" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T465" t="n">
+        <v>24000161</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="B466" t="n">
+        <v>300462</v>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>阴影岛屿-侵入62级</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I466" t="n">
+        <v>62</v>
+      </c>
+      <c r="R466" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S466" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T466" t="n">
+        <v>24000162</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="B467" t="n">
+        <v>300463</v>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>阴影岛屿-侵入63级</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I467" t="n">
+        <v>63</v>
+      </c>
+      <c r="R467" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S467" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T467" t="n">
+        <v>24000163</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="B468" t="n">
+        <v>300464</v>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>阴影岛屿-侵入64级</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I468" t="n">
+        <v>64</v>
+      </c>
+      <c r="R468" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S468" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T468" t="n">
+        <v>24000164</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="B469" t="n">
+        <v>300465</v>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>阴影岛屿-侵入65级</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I469" t="n">
+        <v>65</v>
+      </c>
+      <c r="R469" t="inlineStr">
+        <is>
+          <t>1074,180;106,6</t>
+        </is>
+      </c>
+      <c r="S469" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T469" t="n">
+        <v>24000165</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="B470" t="n">
+        <v>300466</v>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>阴影岛屿-侵入66级</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I470" t="n">
+        <v>66</v>
+      </c>
+      <c r="R470" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S470" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T470" t="n">
+        <v>24000166</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="B471" t="n">
+        <v>300467</v>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>阴影岛屿-侵入67级</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I471" t="n">
+        <v>67</v>
+      </c>
+      <c r="R471" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S471" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T471" t="n">
+        <v>24000167</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="B472" t="n">
+        <v>300468</v>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>阴影岛屿-侵入68级</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I472" t="n">
+        <v>68</v>
+      </c>
+      <c r="R472" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S472" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T472" t="n">
+        <v>24000168</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="B473" t="n">
+        <v>300469</v>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>阴影岛屿-侵入69级</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I473" t="n">
+        <v>69</v>
+      </c>
+      <c r="R473" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S473" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T473" t="n">
+        <v>24000169</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="B474" t="n">
+        <v>300470</v>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>阴影岛屿-侵入70级</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I474" t="n">
+        <v>70</v>
+      </c>
+      <c r="R474" t="inlineStr">
+        <is>
+          <t>1074,280;103,1;2,600</t>
+        </is>
+      </c>
+      <c r="S474" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T474" t="n">
+        <v>24000170</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="B475" t="n">
+        <v>300471</v>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>原始冲动-侵入71级</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I475" t="n">
+        <v>71</v>
+      </c>
+      <c r="R475" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S475" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T475" t="n">
+        <v>24000171</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="B476" t="n">
+        <v>300472</v>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>原始冲动-侵入72级</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I476" t="n">
+        <v>72</v>
+      </c>
+      <c r="R476" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S476" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T476" t="n">
+        <v>24000172</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="B477" t="n">
+        <v>300473</v>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>原始冲动-侵入73级</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I477" t="n">
+        <v>73</v>
+      </c>
+      <c r="R477" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S477" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T477" t="n">
+        <v>24000173</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="B478" t="n">
+        <v>300474</v>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>原始冲动-侵入74级</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I478" t="n">
+        <v>74</v>
+      </c>
+      <c r="R478" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S478" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T478" t="n">
+        <v>24000174</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="B479" t="n">
+        <v>300475</v>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>原始冲动-侵入75级</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I479" t="n">
+        <v>75</v>
+      </c>
+      <c r="R479" t="inlineStr">
+        <is>
+          <t>1074,180;106,6</t>
+        </is>
+      </c>
+      <c r="S479" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T479" t="n">
+        <v>24000175</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="B480" t="n">
+        <v>300476</v>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>原始冲动-侵入76级</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I480" t="n">
+        <v>76</v>
+      </c>
+      <c r="R480" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S480" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T480" t="n">
+        <v>24000176</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="B481" t="n">
+        <v>300477</v>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>原始冲动-侵入77级</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I481" t="n">
+        <v>77</v>
+      </c>
+      <c r="R481" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S481" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T481" t="n">
+        <v>24000177</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="B482" t="n">
+        <v>300478</v>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>原始冲动-侵入78级</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I482" t="n">
+        <v>78</v>
+      </c>
+      <c r="R482" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S482" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T482" t="n">
+        <v>24000178</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="B483" t="n">
+        <v>300479</v>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>原始冲动-侵入79级</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I483" t="n">
+        <v>79</v>
+      </c>
+      <c r="R483" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S483" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T483" t="n">
+        <v>24000179</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="B484" t="n">
+        <v>300480</v>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>原始冲动-侵入80级</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I484" t="n">
+        <v>80</v>
+      </c>
+      <c r="R484" t="inlineStr">
+        <is>
+          <t>1074,280;103,1;2,600;1156,40;1157,3</t>
+        </is>
+      </c>
+      <c r="S484" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T484" t="n">
+        <v>24000180</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="B485" t="n">
+        <v>300481</v>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>本能-侵入81级</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I485" t="n">
+        <v>81</v>
+      </c>
+      <c r="R485" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S485" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T485" t="n">
+        <v>24000181</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="B486" t="n">
+        <v>300482</v>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>本能-侵入82级</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I486" t="n">
+        <v>82</v>
+      </c>
+      <c r="R486" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S486" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T486" t="n">
+        <v>24000182</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="B487" t="n">
+        <v>300483</v>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>本能-侵入83级</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I487" t="n">
+        <v>83</v>
+      </c>
+      <c r="R487" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S487" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T487" t="n">
+        <v>24000183</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="B488" t="n">
+        <v>300484</v>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>本能-侵入84级</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I488" t="n">
+        <v>84</v>
+      </c>
+      <c r="R488" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S488" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T488" t="n">
+        <v>24000184</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="B489" t="n">
+        <v>300485</v>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>本能-侵入85级</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I489" t="n">
+        <v>85</v>
+      </c>
+      <c r="R489" t="inlineStr">
+        <is>
+          <t>1074,180;106,6</t>
+        </is>
+      </c>
+      <c r="S489" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T489" t="n">
+        <v>24000185</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="B490" t="n">
+        <v>300486</v>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>本能-侵入86级</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I490" t="n">
+        <v>86</v>
+      </c>
+      <c r="R490" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S490" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T490" t="n">
+        <v>24000186</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="B491" t="n">
+        <v>300487</v>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>本能-侵入87级</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I491" t="n">
+        <v>87</v>
+      </c>
+      <c r="R491" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S491" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T491" t="n">
+        <v>24000187</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="B492" t="n">
+        <v>300488</v>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>本能-侵入88级</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I492" t="n">
+        <v>88</v>
+      </c>
+      <c r="R492" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S492" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T492" t="n">
+        <v>24000188</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="B493" t="n">
+        <v>300489</v>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>本能-侵入89级</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I493" t="n">
+        <v>89</v>
+      </c>
+      <c r="R493" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S493" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T493" t="n">
+        <v>24000189</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="B494" t="n">
+        <v>300490</v>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>本能-侵入90级</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I494" t="n">
+        <v>90</v>
+      </c>
+      <c r="R494" t="inlineStr">
+        <is>
+          <t>1074,280;103,1;2,600</t>
+        </is>
+      </c>
+      <c r="S494" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T494" t="n">
+        <v>24000190</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="B495" t="n">
+        <v>300491</v>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>真我-侵入91级</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I495" t="n">
+        <v>91</v>
+      </c>
+      <c r="R495" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S495" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T495" t="n">
+        <v>24000191</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="B496" t="n">
+        <v>300492</v>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>真我-侵入92级</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I496" t="n">
+        <v>92</v>
+      </c>
+      <c r="R496" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S496" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T496" t="n">
+        <v>24000192</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="B497" t="n">
+        <v>300493</v>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>真我-侵入93级</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I497" t="n">
+        <v>93</v>
+      </c>
+      <c r="R497" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S497" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T497" t="n">
+        <v>24000193</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="B498" t="n">
+        <v>300494</v>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>真我-侵入94级</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I498" t="n">
+        <v>94</v>
+      </c>
+      <c r="R498" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S498" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T498" t="n">
+        <v>24000194</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="B499" t="n">
+        <v>300495</v>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>真我-侵入95级</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I499" t="n">
+        <v>95</v>
+      </c>
+      <c r="R499" t="inlineStr">
+        <is>
+          <t>1074,180;106,6</t>
+        </is>
+      </c>
+      <c r="S499" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T499" t="n">
+        <v>24000195</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="B500" t="n">
+        <v>300496</v>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>真我-侵入96级</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I500" t="n">
+        <v>96</v>
+      </c>
+      <c r="R500" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S500" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T500" t="n">
+        <v>24000196</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="B501" t="n">
+        <v>300497</v>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>真我-侵入97级</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I501" t="n">
+        <v>97</v>
+      </c>
+      <c r="R501" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S501" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T501" t="n">
+        <v>24000197</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="B502" t="n">
+        <v>300498</v>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>真我-侵入98级</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I502" t="n">
+        <v>98</v>
+      </c>
+      <c r="R502" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S502" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T502" t="n">
+        <v>24000198</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="B503" t="n">
+        <v>300499</v>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>真我-侵入99级</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I503" t="n">
+        <v>99</v>
+      </c>
+      <c r="R503" t="inlineStr">
+        <is>
+          <t>1074,50;2,50</t>
+        </is>
+      </c>
+      <c r="S503" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T503" t="n">
+        <v>24000199</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="B504" t="n">
+        <v>300500</v>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>真我-侵入100级</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>LevelType_PVP</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="I504" t="n">
+        <v>100</v>
+      </c>
+      <c r="R504" t="inlineStr">
+        <is>
+          <t>1074,280;103,1;2,600;1156,40;1157,3;3027,300</t>
+        </is>
+      </c>
+      <c r="S504" t="inlineStr">
+        <is>
+          <t>BLT_Main</t>
+        </is>
+      </c>
+      <c r="T504" t="n">
+        <v>24000200</v>
       </c>
     </row>
   </sheetData>
@@ -27245,7 +30845,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TOWER-20260729-F01</t>
+          <t>TOWER-20260904-F03</t>
         </is>
       </c>
     </row>
@@ -27257,7 +30857,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VALUE_READY_FIRST_ONLY_CHG042</t>
+          <t>VALUE_READY_FIRST_ONLY_CHG044</t>
         </is>
       </c>
     </row>
@@ -27293,7 +30893,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>400条爬塔关卡同步首通引用/预览；每层预览均含房车零件1074，并清空Reward与FallRewardDrop。</t>
+          <t>400条爬塔关卡同步首通引用/预览；40/50/70/80/90层预览追加高级/超高级指南材料；Reward与FallRewardDrop保持清空。</t>
         </is>
       </c>
     </row>
